--- a/result/C202_Test.xlsx
+++ b/result/C202_Test.xlsx
@@ -458,7 +458,7 @@
         <v>591.5599999999999</v>
       </c>
       <c r="E4" s="3">
-        <v>107.09</v>
+        <v>92.3</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -475,7 +475,7 @@
         <v>591.5599999999999</v>
       </c>
       <c r="E5" s="3">
-        <v>85.56</v>
+        <v>95.12</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -492,7 +492,7 @@
         <v>591.5599999999999</v>
       </c>
       <c r="E6" s="3">
-        <v>86.39</v>
+        <v>94.63</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -509,7 +509,7 @@
         <v>591.5599999999999</v>
       </c>
       <c r="E7" s="3">
-        <v>94.09</v>
+        <v>81.33</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -526,7 +526,7 @@
         <v>591.5599999999999</v>
       </c>
       <c r="E8" s="3">
-        <v>90.84</v>
+        <v>75.59999999999999</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -543,7 +543,7 @@
         <v>591.5599999999999</v>
       </c>
       <c r="E9" s="3">
-        <v>91.05</v>
+        <v>74.89</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -560,7 +560,7 @@
         <v>591.5599999999999</v>
       </c>
       <c r="E10" s="3">
-        <v>94.64</v>
+        <v>96.33</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -577,7 +577,7 @@
         <v>591.5599999999999</v>
       </c>
       <c r="E11" s="3">
-        <v>99.98</v>
+        <v>117.12</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -594,7 +594,7 @@
         <v>591.5599999999999</v>
       </c>
       <c r="E12" s="3">
-        <v>83.76000000000001</v>
+        <v>107.96</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -611,7 +611,7 @@
         <v>591.5599999999999</v>
       </c>
       <c r="E13" s="3">
-        <v>82.56</v>
+        <v>108.68</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -628,7 +628,7 @@
         <v>591.5599999999998</v>
       </c>
       <c r="E14" s="3">
-        <v>91.596</v>
+        <v>94.396</v>
       </c>
     </row>
   </sheetData>
